--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-04-2026.xlsx
@@ -931,7 +931,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£25.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>£1209.7</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£42.24</t>
+          <t>£37.24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
